--- a/tasks/finalpool/yf-sf-market-sales-excel-ppt-gcal/groundtruth_workspace/Market_Sales_Correlation.xlsx
+++ b/tasks/finalpool/yf-sf-market-sales-excel-ppt-gcal/groundtruth_workspace/Market_Sales_Correlation.xlsx
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>180</v>
+        <v>218.94</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="3">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>170</v>
+        <v>300.88</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>155</v>
+        <v>239.63</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="5">
@@ -523,7 +523,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JP Morgan Chase</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>293.55</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="6">
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Exxon Mobil Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -555,10 +555,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>110</v>
+        <v>150.76</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1</v>
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,49 +600,193 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>150000</v>
+        <v>130634.57</v>
       </c>
       <c r="C2" t="n">
-        <v>1800</v>
+        <v>797</v>
       </c>
       <c r="D2" t="n">
-        <v>83.33</v>
+        <v>163.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>155000</v>
+        <v>127379.39</v>
       </c>
       <c r="C3" t="n">
-        <v>1850</v>
+        <v>833</v>
       </c>
       <c r="D3" t="n">
-        <v>83.78</v>
+        <v>152.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>160000</v>
+        <v>104099.62</v>
       </c>
       <c r="C4" t="n">
-        <v>1900</v>
+        <v>773</v>
       </c>
       <c r="D4" t="n">
-        <v>84.20999999999999</v>
+        <v>134.67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>120898.58</v>
+      </c>
+      <c r="C5" t="n">
+        <v>809</v>
+      </c>
+      <c r="D5" t="n">
+        <v>149.44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>111374.86</v>
+      </c>
+      <c r="C6" t="n">
+        <v>789</v>
+      </c>
+      <c r="D6" t="n">
+        <v>141.16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>119056.54</v>
+      </c>
+      <c r="C7" t="n">
+        <v>706</v>
+      </c>
+      <c r="D7" t="n">
+        <v>168.64</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>126333.75</v>
+      </c>
+      <c r="C8" t="n">
+        <v>781</v>
+      </c>
+      <c r="D8" t="n">
+        <v>161.76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>118232.96</v>
+      </c>
+      <c r="C9" t="n">
+        <v>821</v>
+      </c>
+      <c r="D9" t="n">
+        <v>144.01</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>132763.25</v>
+      </c>
+      <c r="C10" t="n">
+        <v>826</v>
+      </c>
+      <c r="D10" t="n">
+        <v>160.73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>127327.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>797</v>
+      </c>
+      <c r="D11" t="n">
+        <v>159.76</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>111602.65</v>
+      </c>
+      <c r="C12" t="n">
+        <v>719</v>
+      </c>
+      <c r="D12" t="n">
+        <v>155.22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>13143.24</v>
+      </c>
+      <c r="C13" t="n">
+        <v>102</v>
+      </c>
+      <c r="D13" t="n">
+        <v>128.86</v>
       </c>
     </row>
   </sheetData>
@@ -701,16 +845,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -720,7 +864,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -729,10 +873,10 @@
         <v>0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +886,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C4" t="n">
         <v>0.15</v>
@@ -751,10 +895,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5">
@@ -764,19 +908,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -786,16 +930,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -812,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,68 +979,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tech stocks highly correlated</t>
+          <t>Tech stocks show moderate positive correlation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AMZN-GOOGL: 0.85</t>
+          <t>AMZN-GOOGL correlation around 0.45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Diversification benefit limited within tech</t>
+          <t>Diversification benefit limited within tech sector</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Energy inversely related to tech</t>
+          <t>Energy and tech show low correlation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XOM-AMZN: -0.10</t>
+          <t>XOM-AMZN correlation around 0.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Good diversification pair</t>
+          <t>Good diversification pair across sectors</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financial sector moderate correlation</t>
+          <t>Financial sector moderate correlation with tech</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPM with market: 0.60</t>
+          <t>JPM-AMZN correlation around 0.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Follows broader market trends</t>
+          <t>Follows broader market trends with sector influence</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Healthcare defensive</t>
+          <t>Healthcare defensive positioning</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JNJ low correlation with all</t>
+          <t>JNJ low correlation with all symbols</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Safe haven during volatility</t>
+          <t>Safe haven characteristics during market volatility</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sales trends correlate with broader market sentiment</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Monthly revenue varies with market conditions</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing strategy should align with macro indicators</t>
         </is>
       </c>
     </row>
